--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486694_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486694_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2624</v>
+        <v>0.4898</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3983</v>
+        <v>0.3257</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6607</v>
+        <v>0.1641</v>
       </c>
       <c r="G2" t="n">
         <v>1.6937</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4416</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4693</v>
+        <v>0.2546</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9109</v>
+        <v>0.4143</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3282</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1545</v>
+        <v>0.1793</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1545</v>
+        <v>0.1793</v>
       </c>
       <c r="G3" t="n">
         <v>0.1379</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1782</v>
+        <v>0.128</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6619</v>
+        <v>-0.455</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4837</v>
+        <v>0.5831</v>
       </c>
       <c r="G4" t="n">
         <v>-0.538</v>
@@ -766,13 +766,13 @@
         <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1269</v>
+        <v>0.1793</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0552</v>
+        <v>0.1517</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0717</v>
+        <v>0.0277</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2856</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3442</v>
+        <v>-0.6834</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4547</v>
+        <v>0.041</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.7245</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2142</v>
@@ -844,13 +844,13 @@
         <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5184</v>
+        <v>0.1792</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4688</v>
+        <v>0.0551</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2277</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SOLE MOURATAY</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6079</v>
+        <v>-1.271</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2174</v>
+        <v>-0.8466</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3905</v>
+        <v>-0.4244</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9874</v>
+        <v>-1.6155</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7508</v>
+        <v>-0.8966</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2366</v>
+        <v>-0.7189</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2341</v>
+        <v>0.1509</v>
       </c>
       <c r="K6" t="n">
-        <v>1.181</v>
+        <v>0.759</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4151</v>
+        <v>-0.6081</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7533</v>
+        <v>-1.7664</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9318</v>
+        <v>-1.6555</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1785</v>
+        <v>-0.1108</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.8962</v>
+        <v>0.7723</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.827</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8202</v>
+        <v>0.186</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4887</v>
+        <v>0.2961</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3315</v>
+        <v>-0.1101</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4554</v>
+        <v>-0.6138</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3548</v>
+        <v>-0.3282</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8995</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>M. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0601</v>
+        <v>-1.4111</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5363</v>
+        <v>-1.9547</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.5435</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6155</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8966</v>
+        <v>2.3733</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7189</v>
+        <v>-1.5915</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1509</v>
+        <v>1.9142</v>
       </c>
       <c r="K7" t="n">
-        <v>0.759</v>
+        <v>3.4084</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6081</v>
+        <v>-1.4942</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7664</v>
+        <v>-1.1324</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6555</v>
+        <v>-1.0351</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1108</v>
+        <v>-0.0973</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.397</v>
+        <v>0.1586</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6064000000000001</v>
+        <v>-0.0073</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2095</v>
+        <v>0.1659</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6138</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. YOUNG MEDIERO</t>
+          <t>M. SOLE MOURATAY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4413</v>
+        <v>-1.5595</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8855</v>
+        <v>-1.0448</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4442</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7818000000000001</v>
+        <v>-1.9874</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3733</v>
+        <v>-0.7508</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5915</v>
+        <v>-1.2366</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9142</v>
+        <v>-0.2341</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4084</v>
+        <v>1.181</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4942</v>
+        <v>-1.4151</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1324</v>
+        <v>-1.7533</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0351</v>
+        <v>-1.9318</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0973</v>
+        <v>0.1785</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7377</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8616</v>
+        <v>-4.827</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8715000000000001</v>
+        <v>0.8687</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9381</v>
+        <v>0.6614</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.2073</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6138</v>
+        <v>2.4554</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.3548</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6138</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4797</v>
+        <v>-1.8325</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8894</v>
+        <v>-1.6317</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5903</v>
+        <v>-0.2008</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0917</v>
+        <v>-3.5356</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2891</v>
+        <v>-1.917</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8026</v>
+        <v>-1.6186</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1666</v>
+        <v>-1.6383</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2886</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>-0.6872</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9251</v>
+        <v>-1.8973</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0005</v>
+        <v>-0.9659</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9247</v>
+        <v>-0.9314</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9748</v>
+        <v>0.3515</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3511</v>
+        <v>0.0066</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6237</v>
+        <v>0.3449</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5559</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6806</v>
+        <v>-3.1252</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3556</v>
+        <v>-0.4487</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.325</v>
+        <v>-2.6765</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5356</v>
+        <v>-1.6144</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.917</v>
+        <v>-0.7034</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6186</v>
+        <v>-0.911</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6383</v>
+        <v>-0.5933</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9510999999999999</v>
+        <v>0.0554</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6872</v>
+        <v>-0.6488</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8973</v>
+        <v>-1.0211</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9659</v>
+        <v>-0.7588</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9314</v>
+        <v>-0.2623</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4966</v>
+        <v>0.1723</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7174</v>
+        <v>0.1446</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2208</v>
+        <v>0.0277</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1211</v>
+        <v>-3.4064</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3453</v>
+        <v>-2.7168</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7758</v>
+        <v>-0.6896</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6144</v>
+        <v>-3.0917</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7034</v>
+        <v>-2.2891</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.911</v>
+        <v>-0.8026</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5933</v>
+        <v>-2.1666</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0554</v>
+        <v>-2.2886</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6488</v>
+        <v>0.1221</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0211</v>
+        <v>-0.9251</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7588</v>
+        <v>-0.0005</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2623</v>
+        <v>-0.9247</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1763</v>
+        <v>1.0481</v>
       </c>
       <c r="T11" t="n">
-        <v>0.248</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0717</v>
+        <v>0.5244</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4554</v>
+        <v>-1.5559</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4554</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2165</v>
+        <v>-4.2206</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7454</v>
+        <v>-3.8489</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4711</v>
+        <v>-0.3718</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2566</v>
@@ -1390,13 +1390,13 @@
         <v>0.7723</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2649</v>
+        <v>-0.269</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0825</v>
+        <v>-0.0209</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3474</v>
+        <v>-0.248</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5712</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.7127</v>
+        <v>-16.7126</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.5804</v>
+        <v>-12.5805</v>
       </c>
       <c r="F13" t="n">
         <v>-4.1322</v>
@@ -1441,10 +1441,10 @@
         <v>-4.691</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4727</v>
+        <v>-0.4727000000000006</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4206</v>
+        <v>2.420599999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-2.8933</v>
@@ -1459,7 +1459,7 @@
         <v>-1.7977</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.861699999999999</v>
+        <v>-3.8617</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.3426</v>
@@ -1471,10 +1471,10 @@
         <v>3.585</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0655</v>
+        <v>2.0656</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5195</v>
+        <v>1.5197</v>
       </c>
       <c r="V13" t="n">
         <v>-5.1962</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.222</v>
+        <v>6.106</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7213</v>
+        <v>2.9281</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5007</v>
+        <v>3.1779</v>
       </c>
       <c r="G14" t="n">
         <v>2.8337</v>
@@ -1546,13 +1546,13 @@
         <v>3.2823</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3528</v>
+        <v>-0.4687</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4142</v>
+        <v>-0.2073</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0614</v>
+        <v>-0.2614</v>
       </c>
       <c r="V14" t="n">
         <v>3.3548</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8902</v>
+        <v>4.6875</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9288</v>
+        <v>1.8254</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9614</v>
+        <v>2.8621</v>
       </c>
       <c r="G15" t="n">
         <v>1.9325</v>
@@ -1624,13 +1624,13 @@
         <v>2.8962</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3971</v>
+        <v>-0.5998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1934</v>
+        <v>-0.2969</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2036</v>
+        <v>-0.303</v>
       </c>
       <c r="V15" t="n">
         <v>3.3548</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7726</v>
+        <v>4.0498</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6505</v>
+        <v>2.7539</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1221</v>
+        <v>1.296</v>
       </c>
       <c r="G16" t="n">
         <v>5.3738</v>
@@ -1702,13 +1702,13 @@
         <v>3.6685</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7943</v>
+        <v>-0.5171</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.359</v>
+        <v>-0.2556</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4353</v>
+        <v>-0.2615</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6138</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0136</v>
+        <v>2.5751</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1622</v>
+        <v>-0.2515</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8514</v>
+        <v>2.8266</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1418</v>
@@ -1780,13 +1780,13 @@
         <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6454</v>
+        <v>0.2069</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6616</v>
+        <v>0.2479</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0162</v>
+        <v>-0.041</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3338</v>
+        <v>1.7227</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0025</v>
+        <v>1.4162</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3314</v>
+        <v>0.3065</v>
       </c>
       <c r="G18" t="n">
         <v>2.2745</v>
@@ -1858,13 +1858,13 @@
         <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6784</v>
+        <v>-0.2895</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6622</v>
+        <v>-0.2485</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0162</v>
+        <v>-0.041</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2277</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3587</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3973</v>
+        <v>-2.5007</v>
       </c>
       <c r="F20" t="n">
-        <v>2.756</v>
+        <v>3.0788</v>
       </c>
       <c r="G20" t="n">
         <v>0.8635</v>
@@ -2014,13 +2014,13 @@
         <v>1.9308</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.833</v>
+        <v>-0.6136</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.1865</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7499</v>
+        <v>-0.4271</v>
       </c>
       <c r="V20" t="n">
         <v>0.3282</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. QUINTERO HURTADO</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.144</v>
+        <v>-0.0531</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0073</v>
+        <v>-1.8453</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1513</v>
+        <v>1.7922</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3527</v>
+        <v>-0.9843</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5584</v>
+        <v>-0.8487</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.911</v>
+        <v>-0.1356</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3237</v>
+        <v>-1.0661</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9725</v>
+        <v>-0.5032</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6488</v>
+        <v>-0.5628</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6764</v>
+        <v>0.0818</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4142</v>
+        <v>-0.3454</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2623</v>
+        <v>0.4272</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5792</v>
+        <v>2.3169</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.6827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3311</v>
+        <v>-0.0761</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2485</v>
+        <v>-0.6065</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>J. QUINTERO HURTADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2477</v>
+        <v>-0.1044</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7419</v>
+        <v>-0.0073</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4942</v>
+        <v>-0.097</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9843</v>
+        <v>-0.3527</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8487</v>
+        <v>0.5584</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1356</v>
+        <v>-0.911</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0661</v>
+        <v>0.3237</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5032</v>
+        <v>0.9725</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5628</v>
+        <v>-0.6488</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0818</v>
+        <v>-0.6764</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3454</v>
+        <v>-0.4142</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4272</v>
+        <v>-0.2623</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3169</v>
+        <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8772</v>
+        <v>-0.3309</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0273</v>
+        <v>-0.3311</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9045</v>
+        <v>0.0002</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0909</v>
+        <v>-2.1654</v>
       </c>
       <c r="E24" t="n">
         <v>-1.3583</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7326</v>
+        <v>-0.8071</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1586</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0332</v>
+        <v>-0.0413</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0139</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.71270000000001</v>
+        <v>16.7127</v>
       </c>
       <c r="E25" t="n">
         <v>4.132299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>12.5805</v>
+        <v>12.5806</v>
       </c>
       <c r="G25" t="n">
         <v>11.2399</v>
       </c>
       <c r="H25" t="n">
-        <v>6.548900000000001</v>
+        <v>6.5489</v>
       </c>
       <c r="I25" t="n">
         <v>4.691199999999999</v>
@@ -2380,16 +2380,16 @@
         <v>10.7672</v>
       </c>
       <c r="K25" t="n">
-        <v>8.969600000000002</v>
+        <v>8.9696</v>
       </c>
       <c r="L25" t="n">
-        <v>1.797799999999999</v>
+        <v>1.7978</v>
       </c>
       <c r="M25" t="n">
         <v>0.4727999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.4205</v>
+        <v>-2.420500000000001</v>
       </c>
       <c r="O25" t="n">
         <v>2.8933</v>
@@ -2404,7 +2404,7 @@
         <v>18.3424</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.5851</v>
+        <v>-3.585</v>
       </c>
       <c r="T25" t="n">
         <v>-1.5197</v>
